--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcPrdBaseinfoSubNewExcel.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcPrdBaseinfoSubNewExcel.xlsx
@@ -2,26 +2,74 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+  <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitHome\2.1.7\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12480"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19820" windowHeight="7860"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="产品基本信息" sheetId="3" r:id="rId1"/>
+    <sheet name="产品终止信息" sheetId="2" r:id="rId2"/>
+    <sheet name="填写说明" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="114210"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="234">
+  <si>
+    <t>样式：文本    不允许编辑</t>
+  </si>
+  <si>
+    <t>样式：文本</t>
+  </si>
+  <si>
+    <t>字段长度</t>
+  </si>
+  <si>
+    <t>15c</t>
+  </si>
+  <si>
+    <t>60c</t>
+  </si>
+  <si>
+    <t>10d</t>
+  </si>
+  <si>
+    <t>3c</t>
+  </si>
+  <si>
+    <t>序号</t>
+  </si>
+  <si>
+    <t>产品代码</t>
+  </si>
+  <si>
+    <t>发行机构代码</t>
+  </si>
+  <si>
+    <t>产品名称</t>
+  </si>
+  <si>
+    <t>产品品种</t>
+  </si>
+  <si>
+    <t>产品类型</t>
+  </si>
+  <si>
+    <t>产品品牌</t>
+  </si>
+  <si>
+    <t>产品期次</t>
+  </si>
+  <si>
+    <t>发行机构内部产品代码</t>
+  </si>
   <si>
     <t>募集方式</t>
   </si>
@@ -32,143 +80,728 @@
     <t>运行方式</t>
   </si>
   <si>
+    <t>募集起始日期</t>
+  </si>
+  <si>
+    <t>募集结束日期</t>
+  </si>
+  <si>
+    <t>发行机构提前终止权标识</t>
+  </si>
+  <si>
+    <t>客户赎回权标识</t>
+  </si>
+  <si>
     <t>产品增信标识</t>
   </si>
   <si>
+    <t>境内托管机构代码</t>
+  </si>
+  <si>
+    <t>境外托管机构国别</t>
+  </si>
+  <si>
+    <t>境外托管机构名称</t>
+  </si>
+  <si>
+    <t>产品起始日期</t>
+  </si>
+  <si>
+    <t>产品预计终止日期</t>
+  </si>
+  <si>
+    <t>受托职责</t>
+  </si>
+  <si>
+    <t>分级产品标识</t>
+  </si>
+  <si>
+    <t>收益权转让产品标识</t>
+  </si>
+  <si>
+    <t>货币市场基金标识</t>
+  </si>
+  <si>
+    <t>其他产品标识1</t>
+  </si>
+  <si>
+    <t>其他产品标识2</t>
+  </si>
+  <si>
+    <t>其他产品标识3</t>
+  </si>
+  <si>
+    <t>募集资金币种</t>
+  </si>
+  <si>
+    <t>兑付本金币种</t>
+  </si>
+  <si>
+    <t>兑付收益币种</t>
+  </si>
+  <si>
+    <t>增信机构类型</t>
+  </si>
+  <si>
     <t>增信形式</t>
   </si>
   <si>
-    <t>境内托管机构代码</t>
-  </si>
-  <si>
-    <t>境外托管机构国别</t>
-  </si>
-  <si>
-    <t>产品起始日期</t>
-  </si>
-  <si>
-    <t>产品预计终止日期</t>
-  </si>
-  <si>
-    <t>分级产品标识</t>
-  </si>
-  <si>
-    <t>产品代码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>发行机构代码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品名称</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品品种</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品类型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品品牌</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品期次</t>
-  </si>
-  <si>
-    <t>发行机构内部产品代码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>募集起始日期</t>
-  </si>
-  <si>
-    <t>募集结束日期</t>
-  </si>
-  <si>
-    <t>发行机构提前终止权标识</t>
-  </si>
-  <si>
-    <t>客户赎回权标识</t>
-  </si>
-  <si>
-    <t>境外托管机构名称</t>
-  </si>
-  <si>
-    <t>受托职责</t>
-  </si>
-  <si>
-    <t>收益权转让产品标识</t>
-  </si>
-  <si>
-    <t>货币市场基金标识</t>
-  </si>
-  <si>
-    <t>其他产品标识1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>其他产品标识2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>其他产品标识3</t>
-  </si>
-  <si>
-    <t>募集资金币种</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>兑付本金币种</t>
-  </si>
-  <si>
-    <t>兑付收益币种</t>
-  </si>
-  <si>
-    <t>增信机构类型</t>
+    <t>注：1.标黄字段在数据接入及导入维护信息时，需进行必填校验；
+2.其中增信机构类型和增信形式为选择性必填，只有在“产品增信标识”字段为“是”的时候必填，其余情况下为空。</t>
+  </si>
+  <si>
+    <t>格式：yyyy-mm-dd</t>
+  </si>
+  <si>
+    <t>样式：数字</t>
+  </si>
+  <si>
+    <t>样式：下拉框                  内容:3位字母型代码             选项：GB/T 12406《表示货币和资金的代码》中的三位字母型代码</t>
+  </si>
+  <si>
+    <t>样式：数字     单位：万（元）</t>
+  </si>
+  <si>
+    <t>样式：数字        单位：万元</t>
+  </si>
+  <si>
+    <t>Decimal(8,5)</t>
+  </si>
+  <si>
+    <t>Decimal(18,6)</t>
+  </si>
+  <si>
+    <t>产品实际终止日期</t>
+  </si>
+  <si>
+    <t>兑付客户收益率</t>
+  </si>
+  <si>
+    <t>币种代码</t>
+  </si>
+  <si>
+    <t>兑付客户收益</t>
+  </si>
+  <si>
+    <t>兑付客户收益转人民币</t>
+  </si>
+  <si>
+    <t>注：1.标黄字段在数据接入及导入维护信息时，需进行必填校验</t>
+  </si>
+  <si>
+    <t>币种</t>
+  </si>
+  <si>
+    <t>CNY 人民币</t>
+  </si>
+  <si>
+    <t>HKD 港元</t>
+  </si>
+  <si>
+    <t>USD 美元</t>
+  </si>
+  <si>
+    <t>EUR 欧元</t>
+  </si>
+  <si>
+    <t>JPY 日元</t>
+  </si>
+  <si>
+    <t>MOP 澳门元</t>
+  </si>
+  <si>
+    <t>CHF 瑞士法郎</t>
+  </si>
+  <si>
+    <t>GBP 英镑</t>
+  </si>
+  <si>
+    <t>RUB 俄罗斯卢布</t>
+  </si>
+  <si>
+    <t>CAD 加拿大元</t>
+  </si>
+  <si>
+    <t>DKK 丹麦克朗</t>
+  </si>
+  <si>
+    <t>AUD 澳大利亚元</t>
+  </si>
+  <si>
+    <t>SEK 瑞典克朗</t>
+  </si>
+  <si>
+    <t>SGD 新加坡元</t>
+  </si>
+  <si>
+    <t>TWD 台币</t>
+  </si>
+  <si>
+    <t>AED 阿拉伯联合酋长国迪尔汗</t>
+  </si>
+  <si>
+    <t>AFN 阿富汗阿富汗尼</t>
+  </si>
+  <si>
+    <t>ALL 阿尔巴尼亚列克</t>
+  </si>
+  <si>
+    <t>AMD 亚美尼亚德拉姆</t>
+  </si>
+  <si>
+    <t>ANG 荷属安的列斯盾</t>
+  </si>
+  <si>
+    <t>AOA 安哥拉宽扎</t>
+  </si>
+  <si>
+    <t>ARS 阿根廷比索</t>
+  </si>
+  <si>
+    <t>AWG 阿鲁巴弗罗林</t>
+  </si>
+  <si>
+    <t>AZN 阿塞拜疆马纳特</t>
+  </si>
+  <si>
+    <t>BAM 波斯尼亚和黑塞哥维那可兑换马克</t>
+  </si>
+  <si>
+    <t>BBD 巴巴多斯元</t>
+  </si>
+  <si>
+    <t>BDT 孟加拉塔卡</t>
+  </si>
+  <si>
+    <t>BGN 保加利亚列弗</t>
+  </si>
+  <si>
+    <t>BHD 巴林第纳尔</t>
+  </si>
+  <si>
+    <t>BIF 布隆迪法郎</t>
+  </si>
+  <si>
+    <t>BMD 百慕大元</t>
+  </si>
+  <si>
+    <t>BND 文莱元</t>
+  </si>
+  <si>
+    <t>BOB 玻利维亚诺</t>
+  </si>
+  <si>
+    <t>BOV 玻利维亚Mvdol基金</t>
+  </si>
+  <si>
+    <t>BRL 巴西雷亚尔</t>
+  </si>
+  <si>
+    <t>BSD 巴哈马元</t>
+  </si>
+  <si>
+    <t>BTN 不丹努扎姆</t>
+  </si>
+  <si>
+    <t>BWP 博茨瓦纳普拉</t>
+  </si>
+  <si>
+    <t>BYR 白俄罗斯卢布</t>
+  </si>
+  <si>
+    <t>BZD 伯利兹元</t>
+  </si>
+  <si>
+    <t>CDF 刚果民主共和国刚果法郎</t>
+  </si>
+  <si>
+    <t>CHE WIR欧元</t>
+  </si>
+  <si>
+    <t>CHW WIR法郎</t>
+  </si>
+  <si>
+    <t>CLF 智利UF基金</t>
+  </si>
+  <si>
+    <t>CLP 智利比索</t>
+  </si>
+  <si>
+    <t>COP 哥伦比亚比索</t>
+  </si>
+  <si>
+    <t>COU 哥伦比亚UVR基金</t>
+  </si>
+  <si>
+    <t>CRC 哥斯达黎加科朗</t>
+  </si>
+  <si>
+    <t>CUC 古巴可兑换比索</t>
+  </si>
+  <si>
+    <t>CUF 古巴比索</t>
+  </si>
+  <si>
+    <t>CVE 佛得角埃斯库多</t>
+  </si>
+  <si>
+    <t>CZK 捷克克朗</t>
+  </si>
+  <si>
+    <t>DJF 吉布提法郎</t>
+  </si>
+  <si>
+    <t>DOP 多米尼加比索</t>
+  </si>
+  <si>
+    <t>DZD 阿尔及利亚第纳尔</t>
+  </si>
+  <si>
+    <t>EGP 埃及镑</t>
+  </si>
+  <si>
+    <t>ERN 厄立特里亚纳克法</t>
+  </si>
+  <si>
+    <t>ETB 埃塞俄比亚比尔</t>
+  </si>
+  <si>
+    <t>FJD 斐济元</t>
+  </si>
+  <si>
+    <t>FKP 福克兰镑</t>
+  </si>
+  <si>
+    <t>GEL 格鲁吉亚拉里</t>
+  </si>
+  <si>
+    <t>GHS 加纳塞地</t>
+  </si>
+  <si>
+    <t>GIP 直布罗陀镑</t>
+  </si>
+  <si>
+    <t>GMD 冈比亚达拉西</t>
+  </si>
+  <si>
+    <t>GNF 几内亚法郎</t>
+  </si>
+  <si>
+    <t>GTQ 危地马拉格查尔</t>
+  </si>
+  <si>
+    <t>GYD 圭亚那元</t>
+  </si>
+  <si>
+    <t>HNL 洪都拉斯伦皮拉</t>
+  </si>
+  <si>
+    <t>HRK 克罗地亚库纳</t>
+  </si>
+  <si>
+    <t>HTG 海地古德</t>
+  </si>
+  <si>
+    <t>HUF 匈牙利福林</t>
+  </si>
+  <si>
+    <t>IDR 印度尼西亚卢比</t>
+  </si>
+  <si>
+    <t>ILS 以色列新谢克尔</t>
+  </si>
+  <si>
+    <t>INR 印度卢比</t>
+  </si>
+  <si>
+    <t>IQD 伊拉克第纳尔</t>
+  </si>
+  <si>
+    <t>IRR 伊朗里亚尔</t>
+  </si>
+  <si>
+    <t>ISK 冰岛克朗</t>
+  </si>
+  <si>
+    <t>JMD 牙买加元</t>
+  </si>
+  <si>
+    <t>JOD 约旦第纳尔</t>
+  </si>
+  <si>
+    <t>KES 肯尼迪先令</t>
+  </si>
+  <si>
+    <t>KGS 吉尔吉斯斯坦索姆</t>
+  </si>
+  <si>
+    <t>KHR 柬埔寨瑞尔</t>
+  </si>
+  <si>
+    <t>KMF 科摩罗法郎</t>
+  </si>
+  <si>
+    <t>KPW 朝鲜元</t>
+  </si>
+  <si>
+    <t>KRW 韩元</t>
+  </si>
+  <si>
+    <t>KWD 科威特第纳尔</t>
+  </si>
+  <si>
+    <t>KYD 开曼群岛元</t>
+  </si>
+  <si>
+    <t>KZT 哈萨克斯坦坚戈</t>
+  </si>
+  <si>
+    <t>LAK 老挝基普</t>
+  </si>
+  <si>
+    <t>LBP 黎巴嫩镑</t>
+  </si>
+  <si>
+    <t>LKR 斯里兰卡卢比</t>
+  </si>
+  <si>
+    <t>LRD 利比里亚元</t>
+  </si>
+  <si>
+    <t>LSL 莱索托洛蒂</t>
+  </si>
+  <si>
+    <t>LYD 利比亚第纳尔</t>
+  </si>
+  <si>
+    <t>MAD 摩洛哥迪拉姆</t>
+  </si>
+  <si>
+    <t>MDL 摩尔多瓦列伊</t>
+  </si>
+  <si>
+    <t>MGA 马达加斯加阿里亚里</t>
+  </si>
+  <si>
+    <t>MKD 马其顿代纳尔</t>
+  </si>
+  <si>
+    <t>MMK 缅甸元</t>
+  </si>
+  <si>
+    <t>MNT 蒙古图格里克</t>
+  </si>
+  <si>
+    <t>MRO 毛里塔尼亚乌吉亚</t>
+  </si>
+  <si>
+    <t>MUR 毛里求斯卢比</t>
+  </si>
+  <si>
+    <t>MVR 马尔代夫拉菲亚</t>
+  </si>
+  <si>
+    <t>MWK 马拉维克瓦查</t>
+  </si>
+  <si>
+    <t>MXN 墨西哥比索</t>
+  </si>
+  <si>
+    <t>MXV 墨西哥UDI基金</t>
+  </si>
+  <si>
+    <t>MYR 马来西亚令吉</t>
+  </si>
+  <si>
+    <t>MZN 莫桑比克梅蒂卡尔</t>
+  </si>
+  <si>
+    <t>NAD 纳米比亚元</t>
+  </si>
+  <si>
+    <t>NGN 尼日利亚奈拉</t>
+  </si>
+  <si>
+    <t>NIO 尼加拉瓜科多巴</t>
+  </si>
+  <si>
+    <t>NOK 挪威克朗</t>
+  </si>
+  <si>
+    <t>NPR 尼泊尔卢比</t>
+  </si>
+  <si>
+    <t>NZD 新西兰元</t>
+  </si>
+  <si>
+    <t>OMR 阿曼里亚尔</t>
+  </si>
+  <si>
+    <t>PAB 巴拿马巴波亚</t>
+  </si>
+  <si>
+    <t>PEN 秘鲁新索尔</t>
+  </si>
+  <si>
+    <t>PGK 巴布亚新几内亚基那</t>
+  </si>
+  <si>
+    <t>PHP 菲律宾比索</t>
+  </si>
+  <si>
+    <t>PKR 巴基斯坦卢比</t>
+  </si>
+  <si>
+    <t>PLN 波兰兹罗提</t>
+  </si>
+  <si>
+    <t>PYG 巴拉圭瓜拉尼</t>
+  </si>
+  <si>
+    <t>QAR 卡塔尔里亚尔</t>
+  </si>
+  <si>
+    <t>RON 罗马尼亚列伊</t>
+  </si>
+  <si>
+    <t>RSD 塞尔维亚第纳尔</t>
+  </si>
+  <si>
+    <t>RWF 卢旺达法郎</t>
+  </si>
+  <si>
+    <t>SAR 沙特里亚尔</t>
+  </si>
+  <si>
+    <t>SBD 所罗门群岛元</t>
+  </si>
+  <si>
+    <t>SCR 塞舌尔卢比</t>
+  </si>
+  <si>
+    <t>SDG 苏丹镑</t>
+  </si>
+  <si>
+    <t>SHP 圣赫勒拿镑</t>
+  </si>
+  <si>
+    <t>SLL 塞拉利昂利昂</t>
+  </si>
+  <si>
+    <t>SOS 索马里先令</t>
+  </si>
+  <si>
+    <t>SRD 苏里南元</t>
+  </si>
+  <si>
+    <t>SSP 南苏丹镑</t>
+  </si>
+  <si>
+    <t>STD 圣多美和普林西比多布拉</t>
+  </si>
+  <si>
+    <t>SVC 萨尔瓦多科朗</t>
+  </si>
+  <si>
+    <t>SYP 叙利亚镑</t>
+  </si>
+  <si>
+    <t>SZL 斯威士兰里兰吉尼</t>
+  </si>
+  <si>
+    <t>THB 泰铢</t>
+  </si>
+  <si>
+    <t>TJS 塔吉克斯坦索莫尼</t>
+  </si>
+  <si>
+    <t>TMT 土库曼斯坦马纳特</t>
+  </si>
+  <si>
+    <t>TND 突尼斯第纳尔</t>
+  </si>
+  <si>
+    <t>TOP 汤加潘加</t>
+  </si>
+  <si>
+    <t>TRY 土耳其里拉</t>
+  </si>
+  <si>
+    <t>TTD 特立尼达和多巴哥元</t>
+  </si>
+  <si>
+    <t>TZS 坦桑尼亚先令</t>
+  </si>
+  <si>
+    <t>UAH 乌克兰格里夫尼亚</t>
+  </si>
+  <si>
+    <t>UGX 乌干达先令</t>
+  </si>
+  <si>
+    <t>USN 美元翌日基金</t>
+  </si>
+  <si>
+    <t>UYI 乌拉圭URUIURUI 基金</t>
+  </si>
+  <si>
+    <t>UYU 乌拉圭比索</t>
+  </si>
+  <si>
+    <t>UZS 乌兹别克斯坦苏姆</t>
+  </si>
+  <si>
+    <t>VEB 委内瑞拉博利瓦</t>
+  </si>
+  <si>
+    <t>VND 越南盾</t>
+  </si>
+  <si>
+    <t>VUV 瓦努阿图瓦图</t>
+  </si>
+  <si>
+    <t>WST 萨摩亚塔拉</t>
+  </si>
+  <si>
+    <t>XAF 中非金融合作法郎(中非法郎)</t>
+  </si>
+  <si>
+    <t>XAG 银(一盎司)</t>
+  </si>
+  <si>
+    <t>XAU 金(一盎司)</t>
+  </si>
+  <si>
+    <t>XBA 欧洲混合单位(债券市场单位)</t>
+  </si>
+  <si>
+    <t>XBB 欧洲货市单位(债券市场单位)</t>
+  </si>
+  <si>
+    <t>XBC 欧洲计算单位9(债券市场单位)</t>
+  </si>
+  <si>
+    <t>XBD 欧洲计算单位17(债券市场单位)</t>
+  </si>
+  <si>
+    <t>XCD 东加勒比元</t>
+  </si>
+  <si>
+    <t>XDR 特别提款权(国际货币基金)</t>
+  </si>
+  <si>
+    <t>XOF 非洲金融共同体法郎(西非法郎)</t>
+  </si>
+  <si>
+    <t>XPD 钯(一盎司)</t>
+  </si>
+  <si>
+    <t>XPF 太平洋法兰西共同体法郎(CFP法郎)</t>
+  </si>
+  <si>
+    <t>XPT 铂(一盎司)</t>
+  </si>
+  <si>
+    <t>XSU 厄瓜多尔苏克雷</t>
+  </si>
+  <si>
+    <t>XTS 为测试保留的代码</t>
+  </si>
+  <si>
+    <t>XUA 非洲开发银行账户单位</t>
+  </si>
+  <si>
+    <t>XXX 非货币交易单位</t>
+  </si>
+  <si>
+    <t>YER 也门里亚尔</t>
+  </si>
+  <si>
+    <t>ZAR 南非兰特</t>
+  </si>
+  <si>
+    <t>ZMW 赞比亚克瓦查</t>
+  </si>
+  <si>
+    <t>ZWL 津巴布韦元</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF373737"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -177,8 +810,40 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -199,7 +864,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -241,7 +906,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -276,7 +941,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -451,148 +1116,1243 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AH5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="15.36328125" customWidth="1"/>
+    <col min="3" max="3" width="15.26953125" customWidth="1"/>
+    <col min="4" max="4" width="13.90625" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="14.36328125" customWidth="1"/>
+    <col min="8" max="8" width="17.36328125" customWidth="1"/>
+    <col min="9" max="9" width="19.453125" customWidth="1"/>
+    <col min="10" max="10" width="18.90625" customWidth="1"/>
+    <col min="11" max="11" width="17.08984375" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
+    <col min="13" max="13" width="14.36328125" customWidth="1"/>
+    <col min="14" max="14" width="12.90625" customWidth="1"/>
+    <col min="15" max="15" width="21.08984375" customWidth="1"/>
+    <col min="16" max="17" width="16.26953125" customWidth="1"/>
+    <col min="18" max="18" width="16.7265625" customWidth="1"/>
+    <col min="19" max="19" width="18.90625" customWidth="1"/>
+    <col min="20" max="20" width="14.90625" customWidth="1"/>
+    <col min="21" max="21" width="17.36328125" customWidth="1"/>
+    <col min="22" max="22" width="11.6328125" customWidth="1"/>
+    <col min="23" max="23" width="18" customWidth="1"/>
+    <col min="24" max="24" width="18.6328125" customWidth="1"/>
+    <col min="25" max="25" width="18.90625" customWidth="1"/>
+    <col min="26" max="26" width="17.90625" customWidth="1"/>
+    <col min="27" max="27" width="12.26953125" customWidth="1"/>
+    <col min="28" max="28" width="13.26953125" customWidth="1"/>
+    <col min="29" max="29" width="11.90625" customWidth="1"/>
+    <col min="30" max="30" width="18.26953125" customWidth="1"/>
+    <col min="31" max="31" width="15.453125" customWidth="1"/>
+    <col min="32" max="32" width="14.36328125" customWidth="1"/>
+    <col min="33" max="33" width="20" customWidth="1"/>
+    <col min="34" max="34" width="14.453125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:34" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I1" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="L1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="P1" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>5</v>
-      </c>
-      <c r="R1" t="s">
-        <v>6</v>
-      </c>
-      <c r="S1" t="s">
+      <c r="P1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="T1" t="s">
-        <v>7</v>
-      </c>
-      <c r="U1" t="s">
-        <v>8</v>
-      </c>
-      <c r="V1" t="s">
+      <c r="Q1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="W1" t="s">
-        <v>9</v>
-      </c>
-      <c r="X1" t="s">
+      <c r="R1" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="S1" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="T1" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="U1" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="V1" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="W1" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="X1" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="Y1" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="Z1" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="AG1" t="s">
-        <v>4</v>
-      </c>
+      <c r="AA1" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB1" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC1" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD1" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE1" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF1" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG1" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="AH1" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" ht="43" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="4294963191" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-  <headerFooter alignWithMargins="0"/>
+  <mergeCells count="1">
+    <mergeCell ref="A5:I5"/>
+  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <dataValidations count="10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L4 L6:L13 L14:L65534">
+      <formula1>"1-开放式净值型,2-开放式非净值型,3-封闭式净值型,4-封闭式非净值型"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E4 E6:E13 E14:E65534">
+      <formula1>"1-银行非保本理财"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F4 F6:F13 F14:F65534">
+      <formula1>"1-固定收益类,2-权益类,3-商品及金融衍生品类,4-混合类"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q4 Q6:Q13 Q14:Q65534 X2:X4 X6:X13 X14:X65534 Y6:Z13 Y2:Z4 Y14:Z65534">
+      <formula1>"1-是,2-否"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J4 J6:J13 J14:J65534">
+      <formula1>"1-公开募集,2-非公开募集"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K4 K6:K13 K14:K65534">
+      <formula1>"1-集合管理,2-单独管理"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O4 O6:O13 O14:O65534 P2:P4 P6:P13 P14:P65534">
+      <formula1>"1-有,2-无"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W4 W6:W13 W14:W65534">
+      <formula1>"1-主动管理业务"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG4 AG6:AG13 AG14:AG65534">
+      <formula1>"1-住户,2-广义政府,3-非金融企业,4-金融机构（实体）,6-境外"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH4 AH6:AH13 AH14:AH65534">
+      <formula1>"1-内部增级,2-外部增级"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>填写说明!$A$2:$A$179</xm:f>
+          </x14:formula1>
+          <xm:sqref>AD5:AF5 AD2:AF4 AD6:AF13 AD14:AF65534</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="4294963191" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-  <headerFooter alignWithMargins="0"/>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="15.6328125" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="23.26953125" customWidth="1"/>
+    <col min="5" max="5" width="15.6328125" customWidth="1"/>
+    <col min="6" max="6" width="29" customWidth="1"/>
+    <col min="7" max="7" width="16.7265625" customWidth="1"/>
+    <col min="8" max="8" width="19.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="70" x14ac:dyDescent="0.25">
+      <c r="A1" s="5"/>
+      <c r="B1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A5:E5"/>
+  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>填写说明!$A$2:$A$179</xm:f>
+          </x14:formula1>
+          <xm:sqref>F4:F65536</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="4294963191" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-  <headerFooter alignWithMargins="0"/>
+  <dimension ref="A1:A179"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173" s="3" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcPrdBaseinfoSubNewExcel.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcPrdBaseinfoSubNewExcel.xlsx
@@ -13,36 +13,14 @@
   </bookViews>
   <sheets>
     <sheet name="产品基本信息" sheetId="3" r:id="rId1"/>
-    <sheet name="产品终止信息" sheetId="2" r:id="rId2"/>
-    <sheet name="填写说明" sheetId="4" r:id="rId3"/>
+    <sheet name="填写说明" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="234">
-  <si>
-    <t>样式：文本    不允许编辑</t>
-  </si>
-  <si>
-    <t>样式：文本</t>
-  </si>
-  <si>
-    <t>字段长度</t>
-  </si>
-  <si>
-    <t>15c</t>
-  </si>
-  <si>
-    <t>60c</t>
-  </si>
-  <si>
-    <t>10d</t>
-  </si>
-  <si>
-    <t>3c</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="214">
   <si>
     <t>序号</t>
   </si>
@@ -148,45 +126,6 @@
   <si>
     <t>注：1.标黄字段在数据接入及导入维护信息时，需进行必填校验；
 2.其中增信机构类型和增信形式为选择性必填，只有在“产品增信标识”字段为“是”的时候必填，其余情况下为空。</t>
-  </si>
-  <si>
-    <t>格式：yyyy-mm-dd</t>
-  </si>
-  <si>
-    <t>样式：数字</t>
-  </si>
-  <si>
-    <t>样式：下拉框                  内容:3位字母型代码             选项：GB/T 12406《表示货币和资金的代码》中的三位字母型代码</t>
-  </si>
-  <si>
-    <t>样式：数字     单位：万（元）</t>
-  </si>
-  <si>
-    <t>样式：数字        单位：万元</t>
-  </si>
-  <si>
-    <t>Decimal(8,5)</t>
-  </si>
-  <si>
-    <t>Decimal(18,6)</t>
-  </si>
-  <si>
-    <t>产品实际终止日期</t>
-  </si>
-  <si>
-    <t>兑付客户收益率</t>
-  </si>
-  <si>
-    <t>币种代码</t>
-  </si>
-  <si>
-    <t>兑付客户收益</t>
-  </si>
-  <si>
-    <t>兑付客户收益转人民币</t>
-  </si>
-  <si>
-    <t>注：1.标黄字段在数据接入及导入维护信息时，需进行必填校验</t>
   </si>
   <si>
     <t>币种</t>
@@ -735,14 +674,22 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -750,6 +697,7 @@
       <sz val="11"/>
       <color rgb="FF373737"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -757,12 +705,7 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -810,26 +753,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -840,10 +774,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1159,296 +1093,169 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="N1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="O1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="P1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="Q1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="R1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="S1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="T1" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="U1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="V1" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="W1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="X1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="Y1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="Z1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="T1" s="10" t="s">
+      <c r="AA1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="U1" s="9" t="s">
+      <c r="AB1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="AC1" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="W1" s="9" t="s">
+      <c r="AD1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="X1" s="9" t="s">
+      <c r="AE1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="Y1" s="9" t="s">
+      <c r="AF1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="Z1" s="9" t="s">
+      <c r="AG1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="AA1" s="10" t="s">
+      <c r="AH1" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="AB1" s="10" t="s">
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AD2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" ht="43" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="AC1" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD1" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE1" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF1" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG1" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="AH1" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34" ht="43" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A5:I5"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="10">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L4 L6:L13 L14:L65534">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L4 L6:L13 L14:L65536">
       <formula1>"1-开放式净值型,2-开放式非净值型,3-封闭式净值型,4-封闭式非净值型"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E4 E6:E13 E14:E65534">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E4 E6:E13 E14:E65536">
       <formula1>"1-银行非保本理财"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F4 F6:F13 F14:F65534">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q4 Q6:Q13 Q14:Q65536 X2:X4 X6:X13 X14:X65536 Y6:Z13 Y2:Z4 Y14:Z65536">
+      <formula1>"1-是,2-否"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O4 O6:O13 O14:O65536 P2:P4 P6:P13 P14:P65536">
+      <formula1>"1-有,2-无"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F4 F6:F13 F14:F65536">
       <formula1>"1-固定收益类,2-权益类,3-商品及金融衍生品类,4-混合类"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q4 Q6:Q13 Q14:Q65534 X2:X4 X6:X13 X14:X65534 Y6:Z13 Y2:Z4 Y14:Z65534">
-      <formula1>"1-是,2-否"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J4 J6:J13 J14:J65534">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J4 J6:J13 J14:J65536">
       <formula1>"1-公开募集,2-非公开募集"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K4 K6:K13 K14:K65534">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K4 K6:K13 K14:K65536">
       <formula1>"1-集合管理,2-单独管理"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O4 O6:O13 O14:O65534 P2:P4 P6:P13 P14:P65534">
-      <formula1>"1-有,2-无"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W4 W6:W13 W14:W65534">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W4 W6:W13 W14:W65536">
       <formula1>"1-主动管理业务"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG4 AG6:AG13 AG14:AG65534">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG4 AG6:AG13 AG14:AG65536">
       <formula1>"1-住户,2-广义政府,3-非金融企业,4-金融机构（实体）,6-境外"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH4 AH6:AH13 AH14:AH65534">
-      <formula1>"1-内部增级,2-外部增级"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH65536">
+      <formula1>"1-内部增级,2-外部增级,3-内外增级"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>填写说明!$A$2:$A$179</xm:f>
-          </x14:formula1>
-          <xm:sqref>AD5:AF5 AD2:AF4 AD6:AF13 AD14:AF65534</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="15.6328125" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="23.26953125" customWidth="1"/>
-    <col min="5" max="5" width="15.6328125" customWidth="1"/>
-    <col min="6" max="6" width="29" customWidth="1"/>
-    <col min="7" max="7" width="16.7265625" customWidth="1"/>
-    <col min="8" max="8" width="19.6328125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="70" x14ac:dyDescent="0.25">
-      <c r="A1" s="5"/>
-      <c r="B1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A5:E5"/>
-  </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>填写说明!$A$2:$A$179</xm:f>
-          </x14:formula1>
-          <xm:sqref>F4:F65536</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A179"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
@@ -1458,901 +1265,901 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcPrdBaseinfoSubNewExcel.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcPrdBaseinfoSubNewExcel.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24701"/>
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitHome\2.1.7\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\ZGBS-CP\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{313FD63D-FDA4-4F0C-8969-28DB4035DD2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19820" windowHeight="7860"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="产品基本信息" sheetId="3" r:id="rId1"/>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="216">
   <si>
     <t>序号</t>
   </si>
@@ -95,9 +96,6 @@
   </si>
   <si>
     <t>收益权转让产品标识</t>
-  </si>
-  <si>
-    <t>货币市场基金标识</t>
   </si>
   <si>
     <t>其他产品标识1</t>
@@ -663,12 +661,21 @@
   </si>
   <si>
     <t>ZWL 津巴布韦元</t>
+  </si>
+  <si>
+    <t>货币市场基金或现金管理类产品</t>
+  </si>
+  <si>
+    <t>跨境理财通标识</t>
+  </si>
+  <si>
+    <t>以财产权信托名义开展的资金信托标识</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1054,45 +1061,45 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AH5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AJ5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.26953125" customWidth="1"/>
-    <col min="4" max="4" width="13.90625" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.21875" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" customWidth="1"/>
-    <col min="8" max="8" width="17.36328125" customWidth="1"/>
-    <col min="9" max="9" width="19.453125" customWidth="1"/>
-    <col min="10" max="10" width="18.90625" customWidth="1"/>
-    <col min="11" max="11" width="17.08984375" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" customWidth="1"/>
+    <col min="8" max="8" width="17.33203125" customWidth="1"/>
+    <col min="9" max="9" width="19.44140625" customWidth="1"/>
+    <col min="10" max="10" width="18.88671875" customWidth="1"/>
+    <col min="11" max="11" width="17.109375" customWidth="1"/>
     <col min="12" max="12" width="20" customWidth="1"/>
-    <col min="13" max="13" width="14.36328125" customWidth="1"/>
-    <col min="14" max="14" width="12.90625" customWidth="1"/>
-    <col min="15" max="15" width="21.08984375" customWidth="1"/>
-    <col min="16" max="17" width="16.26953125" customWidth="1"/>
-    <col min="18" max="18" width="16.7265625" customWidth="1"/>
-    <col min="19" max="19" width="18.90625" customWidth="1"/>
-    <col min="20" max="20" width="14.90625" customWidth="1"/>
-    <col min="21" max="21" width="17.36328125" customWidth="1"/>
-    <col min="22" max="22" width="11.6328125" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" customWidth="1"/>
+    <col min="14" max="14" width="12.88671875" customWidth="1"/>
+    <col min="15" max="15" width="21.109375" customWidth="1"/>
+    <col min="16" max="17" width="16.21875" customWidth="1"/>
+    <col min="18" max="18" width="16.77734375" customWidth="1"/>
+    <col min="19" max="19" width="18.88671875" customWidth="1"/>
+    <col min="20" max="20" width="14.88671875" customWidth="1"/>
+    <col min="21" max="21" width="17.33203125" customWidth="1"/>
+    <col min="22" max="22" width="11.6640625" customWidth="1"/>
     <col min="23" max="23" width="18" customWidth="1"/>
-    <col min="24" max="24" width="18.6328125" customWidth="1"/>
-    <col min="25" max="25" width="18.90625" customWidth="1"/>
-    <col min="26" max="26" width="17.90625" customWidth="1"/>
-    <col min="27" max="27" width="12.26953125" customWidth="1"/>
-    <col min="28" max="28" width="13.26953125" customWidth="1"/>
-    <col min="29" max="29" width="11.90625" customWidth="1"/>
-    <col min="30" max="30" width="18.26953125" customWidth="1"/>
-    <col min="31" max="31" width="15.453125" customWidth="1"/>
-    <col min="32" max="32" width="14.36328125" customWidth="1"/>
+    <col min="24" max="24" width="18.6640625" customWidth="1"/>
+    <col min="25" max="25" width="18.88671875" customWidth="1"/>
+    <col min="26" max="26" width="17.88671875" customWidth="1"/>
+    <col min="27" max="27" width="12.21875" customWidth="1"/>
+    <col min="28" max="28" width="13.21875" customWidth="1"/>
+    <col min="29" max="29" width="11.88671875" customWidth="1"/>
+    <col min="30" max="30" width="18.21875" customWidth="1"/>
+    <col min="31" max="31" width="15.44140625" customWidth="1"/>
+    <col min="32" max="32" width="14.33203125" customWidth="1"/>
     <col min="33" max="33" width="20" customWidth="1"/>
-    <col min="34" max="34" width="14.453125" customWidth="1"/>
+    <col min="34" max="34" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1169,41 +1176,47 @@
         <v>24</v>
       </c>
       <c r="Z1" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="AA1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="7" t="s">
+      <c r="AB1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="7" t="s">
+      <c r="AC1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="7" t="s">
+      <c r="AD1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AF1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AG1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="6" t="s">
+      <c r="AH1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AI1" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="AJ1" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AD2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" ht="42.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="AD2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34" ht="43" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>34</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -1220,942 +1233,943 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="10">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L4 L6:L13 L14:L65536">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L4 L6:L13 L14:L65536" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"1-开放式净值型,2-开放式非净值型,3-封闭式净值型,4-封闭式非净值型"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E4 E6:E13 E14:E65536">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E4 E6:E13 E14:E65536" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"1-银行非保本理财"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q4 Q6:Q13 Q14:Q65536 X2:X4 X6:X13 X14:X65536 Y6:Z13 Y2:Z4 Y14:Z65536">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q4 Q6:Q13 Q14:Q65536 X2:X4 X6:X13 X14:X65536 Y6:Z13 Y2:Z4 Y14:Z65536" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"1-是,2-否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O4 O6:O13 O14:O65536 P2:P4 P6:P13 P14:P65536">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O4 O6:O13 O14:O65536 P2:P4 P6:P13 P14:P65536" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"1-有,2-无"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F4 F6:F13 F14:F65536">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F4 F6:F13 F14:F65536" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"1-固定收益类,2-权益类,3-商品及金融衍生品类,4-混合类"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J4 J6:J13 J14:J65536">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J4 J6:J13 J14:J65536" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>"1-公开募集,2-非公开募集"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K4 K6:K13 K14:K65536">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K4 K6:K13 K14:K65536" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>"1-集合管理,2-单独管理"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W4 W6:W13 W14:W65536">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W4 W6:W13 W14:W65536" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>"1-主动管理业务"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG4 AG6:AG13 AG14:AG65536">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG4 AG6:AG13 AG14:AG65536" xr:uid="{00000000-0002-0000-0000-000008000000}">
       <formula1>"1-住户,2-广义政府,3-非金融企业,4-金融机构（实体）,6-境外"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH65536">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH65536" xr:uid="{00000000-0002-0000-0000-000009000000}">
       <formula1>"1-内部增级,2-外部增级,3-内外增级"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A179"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.7265625" customWidth="1"/>
+    <col min="1" max="1" width="26.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcPrdBaseinfoSubNewExcel.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcPrdBaseinfoSubNewExcel.xlsx
@@ -1,27 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24701"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\ZGBS-CP\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitHome\3.0.0\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{313FD63D-FDA4-4F0C-8969-28DB4035DD2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="30940" windowHeight="16900"/>
   </bookViews>
   <sheets>
     <sheet name="产品基本信息" sheetId="3" r:id="rId1"/>
     <sheet name="填写说明" sheetId="4" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="152511" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="214">
   <si>
     <t>序号</t>
   </si>
@@ -96,12 +95,6 @@
   </si>
   <si>
     <t>收益权转让产品标识</t>
-  </si>
-  <si>
-    <t>其他产品标识1</t>
-  </si>
-  <si>
-    <t>其他产品标识2</t>
   </si>
   <si>
     <t>其他产品标识3</t>
@@ -675,7 +668,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1061,45 +1054,43 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AH5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.33203125" customWidth="1"/>
-    <col min="3" max="3" width="15.21875" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" customWidth="1"/>
+    <col min="2" max="2" width="15.36328125" customWidth="1"/>
+    <col min="3" max="3" width="15.1796875" customWidth="1"/>
+    <col min="4" max="4" width="13.90625" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" customWidth="1"/>
-    <col min="8" max="8" width="17.33203125" customWidth="1"/>
-    <col min="9" max="9" width="19.44140625" customWidth="1"/>
-    <col min="10" max="10" width="18.88671875" customWidth="1"/>
-    <col min="11" max="11" width="17.109375" customWidth="1"/>
+    <col min="7" max="7" width="14.36328125" customWidth="1"/>
+    <col min="8" max="8" width="17.36328125" customWidth="1"/>
+    <col min="9" max="9" width="19.453125" customWidth="1"/>
+    <col min="10" max="10" width="18.90625" customWidth="1"/>
+    <col min="11" max="11" width="17.08984375" customWidth="1"/>
     <col min="12" max="12" width="20" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" customWidth="1"/>
-    <col min="14" max="14" width="12.88671875" customWidth="1"/>
-    <col min="15" max="15" width="21.109375" customWidth="1"/>
-    <col min="16" max="17" width="16.21875" customWidth="1"/>
-    <col min="18" max="18" width="16.77734375" customWidth="1"/>
-    <col min="19" max="19" width="18.88671875" customWidth="1"/>
-    <col min="20" max="20" width="14.88671875" customWidth="1"/>
-    <col min="21" max="21" width="17.33203125" customWidth="1"/>
-    <col min="22" max="22" width="11.6640625" customWidth="1"/>
+    <col min="13" max="13" width="14.36328125" customWidth="1"/>
+    <col min="14" max="14" width="12.90625" customWidth="1"/>
+    <col min="15" max="15" width="21.08984375" customWidth="1"/>
+    <col min="16" max="17" width="16.1796875" customWidth="1"/>
+    <col min="18" max="18" width="16.81640625" customWidth="1"/>
+    <col min="19" max="19" width="18.90625" customWidth="1"/>
+    <col min="20" max="20" width="14.90625" customWidth="1"/>
+    <col min="21" max="21" width="17.36328125" customWidth="1"/>
+    <col min="22" max="22" width="11.6328125" customWidth="1"/>
     <col min="23" max="23" width="18" customWidth="1"/>
-    <col min="24" max="24" width="18.6640625" customWidth="1"/>
-    <col min="25" max="25" width="18.88671875" customWidth="1"/>
-    <col min="26" max="26" width="17.88671875" customWidth="1"/>
-    <col min="27" max="27" width="12.21875" customWidth="1"/>
-    <col min="28" max="28" width="13.21875" customWidth="1"/>
-    <col min="29" max="29" width="11.88671875" customWidth="1"/>
-    <col min="30" max="30" width="18.21875" customWidth="1"/>
-    <col min="31" max="31" width="15.44140625" customWidth="1"/>
-    <col min="32" max="32" width="14.33203125" customWidth="1"/>
+    <col min="24" max="24" width="18.6328125" customWidth="1"/>
+    <col min="25" max="25" width="18.90625" customWidth="1"/>
+    <col min="26" max="26" width="17.90625" customWidth="1"/>
+    <col min="29" max="29" width="11.90625" customWidth="1"/>
+    <col min="30" max="30" width="18.1796875" customWidth="1"/>
+    <col min="31" max="31" width="15.453125" customWidth="1"/>
+    <col min="32" max="32" width="14.36328125" customWidth="1"/>
     <col min="33" max="33" width="20" customWidth="1"/>
-    <col min="34" max="34" width="14.44140625" customWidth="1"/>
+    <col min="34" max="34" width="14.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1176,47 +1167,36 @@
         <v>24</v>
       </c>
       <c r="Z1" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="AA1" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="AB1" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="AA1" s="7" t="s">
+      <c r="AC1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="7" t="s">
+      <c r="AD1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="7" t="s">
+      <c r="AE1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AF1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AG1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AH1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" s="6" t="s">
+    </row>
+    <row r="5" spans="1:34" ht="42.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>31</v>
-      </c>
-      <c r="AH1" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI1" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="AJ1" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="AD2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:36" ht="42.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>33</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -1233,34 +1213,34 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="10">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L4 L6:L13 L14:L65536" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L4 L6:L13 L14:L65536">
       <formula1>"1-开放式净值型,2-开放式非净值型,3-封闭式净值型,4-封闭式非净值型"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E4 E6:E13 E14:E65536" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E4 E6:E13 E14:E65536">
       <formula1>"1-银行非保本理财"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q4 Q6:Q13 Q14:Q65536 X2:X4 X6:X13 X14:X65536 Y6:Z13 Y2:Z4 Y14:Z65536" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q4 Q6:Q13 Q14:Q65536 X2:X4 X6:X13 X14:X65536 Y6:Z13 Y2:Z4 Y14:Z65536">
       <formula1>"1-是,2-否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O4 O6:O13 O14:O65536 P2:P4 P6:P13 P14:P65536" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O4 O6:O13 O14:O65536 P2:P4 P6:P13 P14:P65536">
       <formula1>"1-有,2-无"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F4 F6:F13 F14:F65536" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F4 F6:F13 F14:F65536">
       <formula1>"1-固定收益类,2-权益类,3-商品及金融衍生品类,4-混合类"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J4 J6:J13 J14:J65536" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J4 J6:J13 J14:J65536">
       <formula1>"1-公开募集,2-非公开募集"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K4 K6:K13 K14:K65536" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K4 K6:K13 K14:K65536">
       <formula1>"1-集合管理,2-单独管理"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W4 W6:W13 W14:W65536" xr:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W4 W6:W13 W14:W65536">
       <formula1>"1-主动管理业务"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG4 AG6:AG13 AG14:AG65536" xr:uid="{00000000-0002-0000-0000-000008000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG4 AG6:AG13 AG14:AG65536">
       <formula1>"1-住户,2-广义政府,3-非金融企业,4-金融机构（实体）,6-境外"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH65536" xr:uid="{00000000-0002-0000-0000-000009000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH65536">
       <formula1>"1-内部增级,2-外部增级,3-内外增级"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1270,906 +1250,906 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A179"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.77734375" customWidth="1"/>
+    <col min="1" max="1" width="26.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcPrdBaseinfoSubNewExcel.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcPrdBaseinfoSubNewExcel.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24931"/>
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitHome\3.0.0\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\GZYH\zgbszz-guangzhouyinghang\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE5DB0C3-A10C-48AC-87AD-854862B46962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="30940" windowHeight="16900"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="产品基本信息" sheetId="3" r:id="rId1"/>
     <sheet name="填写说明" sheetId="4" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="152511" concurrentCalc="0"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="214">
   <si>
     <t>序号</t>
   </si>
@@ -668,7 +669,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1054,40 +1055,42 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AH5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.1796875" customWidth="1"/>
-    <col min="4" max="4" width="13.90625" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.21875" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" customWidth="1"/>
-    <col min="8" max="8" width="17.36328125" customWidth="1"/>
-    <col min="9" max="9" width="19.453125" customWidth="1"/>
-    <col min="10" max="10" width="18.90625" customWidth="1"/>
-    <col min="11" max="11" width="17.08984375" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" customWidth="1"/>
+    <col min="8" max="8" width="17.33203125" customWidth="1"/>
+    <col min="9" max="9" width="19.44140625" customWidth="1"/>
+    <col min="10" max="10" width="18.88671875" customWidth="1"/>
+    <col min="11" max="11" width="17.109375" customWidth="1"/>
     <col min="12" max="12" width="20" customWidth="1"/>
-    <col min="13" max="13" width="14.36328125" customWidth="1"/>
-    <col min="14" max="14" width="12.90625" customWidth="1"/>
-    <col min="15" max="15" width="21.08984375" customWidth="1"/>
-    <col min="16" max="17" width="16.1796875" customWidth="1"/>
-    <col min="18" max="18" width="16.81640625" customWidth="1"/>
-    <col min="19" max="19" width="18.90625" customWidth="1"/>
-    <col min="20" max="20" width="14.90625" customWidth="1"/>
-    <col min="21" max="21" width="17.36328125" customWidth="1"/>
-    <col min="22" max="22" width="11.6328125" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" customWidth="1"/>
+    <col min="14" max="14" width="12.88671875" customWidth="1"/>
+    <col min="15" max="15" width="21.109375" customWidth="1"/>
+    <col min="16" max="17" width="16.21875" customWidth="1"/>
+    <col min="18" max="18" width="16.77734375" customWidth="1"/>
+    <col min="19" max="19" width="18.88671875" customWidth="1"/>
+    <col min="20" max="20" width="14.88671875" customWidth="1"/>
+    <col min="21" max="21" width="17.33203125" customWidth="1"/>
+    <col min="22" max="22" width="11.6640625" customWidth="1"/>
     <col min="23" max="23" width="18" customWidth="1"/>
-    <col min="24" max="24" width="18.6328125" customWidth="1"/>
-    <col min="25" max="25" width="18.90625" customWidth="1"/>
-    <col min="26" max="26" width="17.90625" customWidth="1"/>
-    <col min="29" max="29" width="11.90625" customWidth="1"/>
-    <col min="30" max="30" width="18.1796875" customWidth="1"/>
-    <col min="31" max="31" width="15.453125" customWidth="1"/>
-    <col min="32" max="32" width="14.36328125" customWidth="1"/>
-    <col min="33" max="33" width="20" customWidth="1"/>
-    <col min="34" max="34" width="14.453125" customWidth="1"/>
+    <col min="24" max="24" width="18.6640625" customWidth="1"/>
+    <col min="25" max="25" width="18.88671875" customWidth="1"/>
+    <col min="26" max="26" width="17.88671875" customWidth="1"/>
+    <col min="27" max="27" width="11.88671875" customWidth="1"/>
+    <col min="28" max="28" width="18.21875" customWidth="1"/>
+    <col min="29" max="29" width="15.44140625" customWidth="1"/>
+    <col min="30" max="30" width="14.33203125" customWidth="1"/>
+    <col min="31" max="31" width="20" customWidth="1"/>
+    <col min="32" max="32" width="14.44140625" customWidth="1"/>
+    <col min="33" max="33" width="17.77734375" customWidth="1"/>
+    <col min="34" max="34" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1169,29 +1172,34 @@
       <c r="Z1" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AA1" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AH1" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="AC1" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD1" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE1" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="AF1" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="AG1" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="AH1" s="6" t="s">
-        <v>30</v>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AB2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:34" ht="42.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -1213,34 +1221,34 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="10">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L4 L6:L13 L14:L65536">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L4 L6:L13 L14:L65536" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"1-开放式净值型,2-开放式非净值型,3-封闭式净值型,4-封闭式非净值型"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E4 E6:E13 E14:E65536">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E4 E6:E13 E14:E65536" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"1-银行非保本理财"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q4 Q6:Q13 Q14:Q65536 X2:X4 X6:X13 X14:X65536 Y6:Z13 Y2:Z4 Y14:Z65536">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q4 Q6:Q13 Q14:Q65536 X2:X4 X6:X13 X14:X65536 Y6:Z13 Y2:Z4 Y14:Z65536 AG1:AG1048576 AH1:AH1048576" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"1-是,2-否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O4 O6:O13 O14:O65536 P2:P4 P6:P13 P14:P65536">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O4 O6:O13 O14:O65536 P2:P4 P6:P13 P14:P65536" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"1-有,2-无"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F4 F6:F13 F14:F65536">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F4 F6:F13 F14:F65536" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"1-固定收益类,2-权益类,3-商品及金融衍生品类,4-混合类"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J4 J6:J13 J14:J65536">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J4 J6:J13 J14:J65536" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>"1-公开募集,2-非公开募集"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K4 K6:K13 K14:K65536">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K4 K6:K13 K14:K65536" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>"1-集合管理,2-单独管理"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W4 W6:W13 W14:W65536">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W4 W6:W13 W14:W65536" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>"1-主动管理业务"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG4 AG6:AG13 AG14:AG65536">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2:AE4 AE6:AE13 AE14:AE65536" xr:uid="{00000000-0002-0000-0000-000008000000}">
       <formula1>"1-住户,2-广义政府,3-非金融企业,4-金融机构（实体）,6-境外"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH65536">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF65536" xr:uid="{00000000-0002-0000-0000-000009000000}">
       <formula1>"1-内部增级,2-外部增级,3-内外增级"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1250,11 +1258,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A179"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.81640625" customWidth="1"/>
+    <col min="1" max="1" width="26.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
